--- a/reports/visit_details/visit_details_nkosingiphile-ntombikayise-ntombi-khumalo.xlsx
+++ b/reports/visit_details/visit_details_nkosingiphile-ntombikayise-ntombi-khumalo.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3046,6 +3046,50 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>7603258963075</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Oupa Mkhanyiswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>7608268963072</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Phindile Masuku</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/visit_details/visit_details_nkosingiphile-ntombikayise-ntombi-khumalo.xlsx
+++ b/reports/visit_details/visit_details_nkosingiphile-ntombikayise-ntombi-khumalo.xlsx
@@ -419,11 +419,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
   </cols>
@@ -3090,6 +3090,3878 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0302026953082</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Njabulo Makhosini</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0112256932085</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Siphosethu Mdlalose</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>7610122365089</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Lerato Mosia</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>7505263590821</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Itumeleng Mosia</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>6209052786092</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Ouma Mosia</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>6309018697063</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Tshepo Lesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>6412296587061</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Moleboheng Lesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>0309268536089</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Relebohile Mofokeng</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0608258746089</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Karabo Mdlalose</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>71081705083</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Novah Mkombo</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>7605235789063</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Mphonyana Moeti</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>6209278695088</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Mohale Moeti</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>7101080376089</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Fikile Tshongwe</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>6512236987072</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Mapula Moeti</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0206062356084</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Atlehang Lesiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>9407035496080</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Skhumbuzo Ndangamandla</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>FN296173</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Ndondena Moyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>5501055542080</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Mandla Sibeko</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>8405071213089</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Nonkululeko Mkhondo</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0209080712089</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Thubelihle Nkambule</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>8904050612085</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Khethukuthula Masuku</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>9704070612083</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Khomotso Bopape</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>8902275448081</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Xolani Gcado</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>8405060512089</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Goodness Chale</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0403150512083</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Jay motloung</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>9501125337087</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Robert Msimango</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>8903040512081</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Precious Mbhele</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0504120512081</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Mandisa Nsibande</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0405030512083</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Kgadi Kgadiey</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>9804150812083</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Florah Bopape</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>7804054556089</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Sthembiso Masuku</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>8704050613089</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Steven Senamolela</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>9904294512089</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Tshepang Pilani</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>8703030512089</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Refelwe Moabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>0005090812089</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Sihle Campbell</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>8604050712089</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Mbongeni Zindi</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>8005060928081</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Tebogo Moagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>9210115267087</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Vusi Moloi</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>0106215986089</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Percy Tsottetsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>0408030512086</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Lindokuhle Tshabalala</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>0302280886086</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Disebo Mofokeng</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>9608050146085</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Thabiso Fuleni</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>8812030840082</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Thoko Mofokeng</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>0205210990642</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Nthabiseng Molata</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>04080305120</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Lindokuhle Shabalala</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>0301115571087</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Sipho Zondo</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>9406145737086</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Mfuno Mbatha</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>8904155446086</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Lungani Mashinini</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Tebogo Miya</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>77072156000084</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Tebogo Seele</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>7508238697042</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Simphiwe Majozi</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>9603298740621</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Nonka Majozi</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>9506238705631</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Itumeleng Majozi</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>9908075869073</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Kgomotso Mahlatsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>9209125874069</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Amanda Twala</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>9608085890632</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Nkululeko Twala</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>95062985096321</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Mpilonhle Twala</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>7612115876093</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Micheal Masuku</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>7508288963052</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Joyce Masuku</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>0302026935093</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Thando Mavundla</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>0302258746051</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Nonhlanhla Mavundla</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>0206236958044</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Gugulethu Mavundla</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>0405086633088</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Zweli Mkhize</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>0102235699082</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Banele Mkhize</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0603258663092</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Sabelo Ngwenya</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>9105263695075</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Khethiwe Ngwenya</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>9308265896062</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Kgosiame Tladi</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>9508296895043</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Nombulelo Mkhathini</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>7902080512089</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Lusapho Mgcina</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>9705030613086</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Lukhona Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>0608080712081</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Nomfundo Motha</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>8307050612089</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Amahle Makhaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>79080905</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Amanda Vilakazi</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>0305070412081</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Kamohelo Dlamini</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>0409070512983</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Zanele Molibeli</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>9507094513089</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Nonkanyiso Ndaba</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>0505030708089</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Karabo Mokhanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>0408256328063</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Nolwazi Mbatha</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>0602235698051</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Nkazimulo Nyembe</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>0204027854856</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Tyson Tsoka</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>0302016789543</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Nosipho Solundwana</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>9611126578876</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Thando Tshabalala</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>5608097654334</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Lonwabo Tshezi</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>9706167890543</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Bongani Makhubo</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>0302166547890</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Gauta Mbokane</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>9908156587120</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Thando Mavuso</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>0406025412088</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Mduduzi Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>9807125678903</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Tebogo Bosahielo</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>324222050</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Ziphozonke Duma</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>8401195768907</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Themba Magasela</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>8401195435671</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Sthembile Magasela</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>9712123565806</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Sphiwe Jekezi9712123456780</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>0303092654680</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Ayanda Mlangeni</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>9611123546789</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Busa Kheswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>9604300990082</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Mbali Makhubu</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>9210045946080</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Siphamandla Mathenjwa</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>8608040991087</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Nelisiwe Ndlovu</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>9605236958041</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Xolile Mabaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>7302269847063</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Nokuthula Ndlovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>7211123586093</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Ayanda Twala</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>0403090512089</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Sinqobile Xulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>0302070412089</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Innocencia Kubheka</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>8704054513083</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Nokuthula Mavimbhela</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>0405060512079</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Luthando Sishwili</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>0304150513083</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Lulamani Zungu</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>0204050312083</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Nomfundo Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>7604066506189</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Johannes Peu</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>0405060512083</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Sphesihle Zondi</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>0304040512082</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Bayanda Buthelezi</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>0209080312083</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Lulamani Zulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>0004040213089</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Sthandiwe Mngomezulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>6703047814089</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Mpiliza Masuku</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>9906050714089</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Thomas Tsotsetsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>0203040312089</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Siphesonke Hlabisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>7804034512083</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Gloria Nkuna</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>7605045613083</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Nhlonipho Zulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>0208173546120</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Lebohang Jase</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>0312034567889</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Kamogelo Motaung</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>1909307615678</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Dickson Segelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>9601112356128</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Sandile Lephoto</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>9704125468897</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Franks Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>9206123651267</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Thando Mavuso</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>060223536082</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Tshiamo Ceba</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>0609258690421</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Lerato Motloung</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>0201286932089</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Sfiso Mbatha</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>0302055289053</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Simphiwe Maluleke</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>6308268540963</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Nkanyiso Yeni</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>7803062589063</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Sabelo Mavimbela</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>7202038569073</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Thando Mavimbela</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>0306286987063</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Keamogetswe Mosia</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>0205258690863</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Zinhle Twala</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>9805052589063</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Sanele Twala</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>7608258963076</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Mampho Moshate</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>7208076890423</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Dieketseng Moshate</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>7708286987066</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Refilwe Moshate</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>0209296587065</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Omphile Moshate</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>0301275806391</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Amanda Mavundla</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>0206258690413</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Njabulo Mavundla</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>0302092758093</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Mpilonhle Mabaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>0112275836908</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Amukelani Ndiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>7611125890632</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Ernest Ndiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>7112236547093</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Maria Ndiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>AB1953405</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Domingo Nxumalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>0312165425082</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Dakalo Raphalala</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>9609156267089</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Nhlanhla Makhalime</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>8609293786061</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Phindile Dlamini</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>0509036456085</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Naledi Nthunya</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>6309305635052</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Lwazi Dlamini</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>7612305860423</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Indiphile Dutywa</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>7611268069042</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Bafana Dutywa</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>7906208630923</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Sphamandla Dutywa</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>8304054513081</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Zinhle Simelane</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>0596070812083</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Nontobeko Nxumalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>8706054513089</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Phumelele Zungu</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>84052345089</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Zolile Nani</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>7804454513089</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Agreneeth Mandonsela</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>89040548089</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Mazwi Ngwenya</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>83090748089</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Nhlanhla Dladla</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>87080549083</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Anna Kgotlele</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>8507054613089</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Syabonga Mtshali</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>910617053089</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Lwazi Mposula</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>7905030714089</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Sibongile Aumuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>8909074913083</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Simphiwe Mlangeni</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>9107024513081</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Seiapati Motloung</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>9106170413083</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Dieketseng motloung</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>0403280512089</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Luyanda Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>8704034512089</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Teboho motloung</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>8605044512083</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Mvelo Mbuyazi</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>96042056081</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Nokuthula Ruralani</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>9403236713083</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Mmabatho Hloelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>9804054512089</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Sifiso Ngwane</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>8706120513089</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Solomon motloung</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>78092345012083</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Mduduzi Kunene</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>8504254512089</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Lulama Mseleku</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>8706054612089</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Mmuso Makhasane</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Nkosingiphile Ntombikayise Ntombi Khumalo</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>8807155481088</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Vusumuzi Mtimuny3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
